--- a/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Cost Centers</t>
+          <t>Forms Sync Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KNVCMMTATJ27BJ6M5DEHZZMC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01KNVCMMTATJ27BJ6M5DEHZZMC</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KNVCMMTATJ27BJ6M5DEHZZMC</t>
+          <t>h_01KNVEEHF11NVNFABDWDV21AEG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01KNVCMMTATJ27BJ6M5DEHZZMC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01KNVEEHF11NVNFABDWDV21AEG</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Success Notifications</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Failure Notifications</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -947,108 +947,64 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-iCIMS-Forms-Sync-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-iCIMS-Forms-Sync-Integration-Guide/headings.xlsx
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Form Upload Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
